--- a/output/pdf_financials_xlsx/FWZ.xlsx
+++ b/output/pdf_financials_xlsx/FWZ.xlsx
@@ -943,13 +943,13 @@
         <v>-13.535401</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>33.264051</v>
+        <v>-33.264051</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>41.74592</v>
+        <v>-41.74592</v>
       </c>
     </row>
     <row r="17">
@@ -1115,13 +1115,13 @@
         <v>-13.535401</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>33.264051</v>
+        <v>-33.264051</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>41.74592</v>
+        <v>-41.74592</v>
       </c>
     </row>
     <row r="21">
@@ -1217,13 +1217,13 @@
         <v>-13.535401</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>33.264051</v>
+        <v>-33.264051</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>41.74592</v>
+        <v>-41.74592</v>
       </c>
     </row>
     <row r="24">
@@ -1319,13 +1319,13 @@
         <v>90.236007</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>138.600212</v>
+        <v>-138.600212</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>165.054924</v>
+        <v>-165.054924</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>198.790095</v>
+        <v>-198.790095</v>
       </c>
     </row>
     <row r="27">
@@ -1353,13 +1353,13 @@
         <v>-13.535401</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>33.264051</v>
+        <v>-33.264051</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>41.74592</v>
+        <v>-41.74592</v>
       </c>
     </row>
     <row r="28">
@@ -1421,13 +1421,13 @@
         <v>-13.4949</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>33.713905</v>
+        <v>-32.814197</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.337332</v>
+        <v>-33.985736</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>42.267524</v>
+        <v>-41.224316</v>
       </c>
     </row>
     <row r="30">
@@ -1507,13 +1507,13 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3635,28 +3635,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.105565</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.222832</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.13391</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.172187</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.351145</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.183253</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.183253</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.183253</v>
       </c>
     </row>
     <row r="93">
@@ -6297,7 +6297,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -7544,7 +7548,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -8673,7 +8681,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -9094,7 +9106,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -9653,7 +9669,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -26224,10 +26244,10 @@
         </is>
       </c>
       <c r="L350" s="5" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>41.74592</v>
+        <v>-41.74592</v>
       </c>
     </row>
     <row r="351">
@@ -27277,10 +27297,10 @@
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>33.264051</v>
+        <v>-33.264051</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>34.661534</v>
+        <v>-34.661534</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FWZ.xlsx
+++ b/output/pdf_financials_xlsx/FWZ.xlsx
@@ -792,28 +792,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.01371</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.110025</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.071022</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.032203</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.306148</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-1.543396</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-1.186933</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-1.028482</v>
       </c>
     </row>
     <row r="13">
@@ -1338,28 +1338,28 @@
         <v>-0.188639</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.959487</v>
+        <v>-0.973197</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.521734</v>
+        <v>-1.631759</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.948397</v>
+        <v>-1.019419</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.922174</v>
+        <v>-8.954376999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-13.535401</v>
+        <v>-13.841549</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-33.264051</v>
+        <v>-31.720655</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-34.661534</v>
+        <v>-33.474601</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-41.74592</v>
+        <v>-40.717438</v>
       </c>
     </row>
     <row r="28">
@@ -1406,28 +1406,28 @@
         <v>-0.188639</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9533430000000001</v>
+        <v>-0.9670530000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.514142</v>
+        <v>-1.624167</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.942546</v>
+        <v>-1.013568</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.879429</v>
+        <v>-8.911632000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-13.4949</v>
+        <v>-13.801048</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-32.814197</v>
+        <v>-31.270801</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-33.985736</v>
+        <v>-32.798803</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-41.224316</v>
+        <v>-40.195834</v>
       </c>
     </row>
     <row r="30">
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.072214</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.179634</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.575784</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.783789</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.179833</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>39.885979</v>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.072214</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.179634</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.575784</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.783789</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.179833</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>39.885979</v>
@@ -2058,19 +2058,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.07416399999999999</v>
+        <v>0.00195</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.261522</v>
+        <v>0.081888</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.737415</v>
+        <v>0.161631</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.934959</v>
+        <v>0.15117</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.393577000000001</v>
+        <v>0.213744</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.174133</v>
@@ -4708,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011266</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027144</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -4723,13 +4723,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.382222</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.50963</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.185734</v>
       </c>
     </row>
     <row r="125">
@@ -4742,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011266</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027144</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -4757,13 +4757,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.382222</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.50963</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.185734</v>
       </c>
     </row>
     <row r="126">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -11192,7 +11192,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -14558,7 +14562,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -17367,7 +17375,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -22888,7 +22900,11 @@
           <t>Lease payments 6</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -25607,7 +25623,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -26081,7 +26097,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -26663,7 +26679,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -27139,7 +27155,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -27853,7 +27869,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">

--- a/output/pdf_financials_xlsx/FWZ.xlsx
+++ b/output/pdf_financials_xlsx/FWZ.xlsx
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.006853</v>
+        <v>0.007189</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.239012</v>
+        <v>0.255525</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.969129</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.006853</v>
+        <v>0.007189</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.973086</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.006853</v>
+        <v>-0.007189</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.973086</v>
@@ -2659,16 +2659,16 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.000436</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.888235</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>2.338882</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>2.736067</v>
       </c>
     </row>
     <row r="65">
@@ -4275,19 +4275,19 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.097773</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03083</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-1.416245</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.25116</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-1.006745</v>
       </c>
     </row>
     <row r="112">
@@ -5075,19 +5075,19 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.097773</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03083</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-1.416245</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.25116</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-1.006745</v>
       </c>
     </row>
     <row r="135">
@@ -5109,19 +5109,19 @@
         <v>-1.152873</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-8.748068</v>
+        <v>-8.845841</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-14.978928</v>
+        <v>-15.009758</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-36.505156</v>
+        <v>-37.921401</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-40.751313</v>
+        <v>-41.002473</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-52.714875</v>
+        <v>-53.72162</v>
       </c>
     </row>
   </sheetData>
@@ -10582,7 +10582,11 @@
           <t>Acquisition of equipment 7</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -10889,7 +10893,11 @@
           <t>Proceeds from share issuance 12</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -14035,7 +14043,11 @@
           <t>Acquisition of equipment 5</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -14261,7 +14273,11 @@
           <t>Proceeds from share issuance 11</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -16966,7 +16982,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -17145,7 +17165,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -29578,7 +29602,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
         <v>0.000336</v>
       </c>
@@ -29881,7 +29909,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
